--- a/public/data/monthly-revenue-11508.xlsx
+++ b/public/data/monthly-revenue-11508.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -867,10 +867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>晶呈科技</v>
+        <v>材料*-KY</v>
       </c>
       <c r="B12" t="str">
-        <v>晶呈科技</v>
+        <v>材料*-KY</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -908,10 +908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>聖暉*</v>
+        <v>晶呈科技</v>
       </c>
       <c r="B13" t="str">
-        <v>聖暉*</v>
+        <v>晶呈科技</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -949,10 +949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>桓鼎-KY</v>
+        <v>聖暉*</v>
       </c>
       <c r="B14" t="str">
-        <v>桓鼎-KY</v>
+        <v>聖暉*</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -990,10 +990,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>朋億*</v>
+        <v>桓鼎-KY</v>
       </c>
       <c r="B15" t="str">
-        <v>朋億*</v>
+        <v>桓鼎-KY</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -1031,10 +1031,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>聯純</v>
+        <v>朋億*</v>
       </c>
       <c r="B16" t="str">
-        <v>聯純</v>
+        <v>朋億*</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>藍新資訊</v>
+        <v>聯純</v>
       </c>
       <c r="B17" t="str">
-        <v>藍新資訊</v>
+        <v>聯純</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>華勝-KY</v>
+        <v>藍新資訊</v>
       </c>
       <c r="B18" t="str">
-        <v>華勝-KY</v>
+        <v>藍新資訊</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -1154,10 +1154,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>樺緯物聯</v>
+        <v>華勝-KY</v>
       </c>
       <c r="B19" t="str">
-        <v>樺緯物聯</v>
+        <v>華勝-KY</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>達運光電</v>
+        <v>樺緯物聯</v>
       </c>
       <c r="B20" t="str">
-        <v>達運光電</v>
+        <v>樺緯物聯</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>銘旺科</v>
+        <v>達運光電</v>
       </c>
       <c r="B21" t="str">
-        <v>銘旺科</v>
+        <v>達運光電</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>擎亞</v>
+        <v>銘旺科</v>
       </c>
       <c r="B22" t="str">
-        <v>擎亞</v>
+        <v>銘旺科</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>豊漁</v>
+        <v>擎亞</v>
       </c>
       <c r="B23" t="str">
-        <v>豊漁</v>
+        <v>擎亞</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>振大環球</v>
+        <v>豊漁</v>
       </c>
       <c r="B24" t="str">
-        <v>振大環球</v>
+        <v>豊漁</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -1400,10 +1400,10 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>佐茂</v>
+        <v>振大環球</v>
       </c>
       <c r="B25" t="str">
-        <v>佐茂</v>
+        <v>振大環球</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -1441,10 +1441,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2330</v>
+        <v>佐茂</v>
       </c>
       <c r="B26" t="str">
-        <v>2330</v>
+        <v>佐茂</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -1482,10 +1482,10 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>3135</v>
+        <v>2330</v>
       </c>
       <c r="B27" t="str">
-        <v>3135</v>
+        <v>2330</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -1523,48 +1523,89 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
+        <v>3135</v>
+      </c>
+      <c r="B28" t="str">
+        <v>3135</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v>11508</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
         <v>8112</v>
       </c>
-      <c r="B28" t="str">
+      <c r="B29" t="str">
         <v>8112</v>
       </c>
-      <c r="C28" t="str">
-        <v/>
-      </c>
-      <c r="D28" t="str">
-        <v>11508</v>
-      </c>
-      <c r="E28" t="str">
-        <v/>
-      </c>
-      <c r="F28" t="str">
-        <v/>
-      </c>
-      <c r="G28" t="str">
-        <v/>
-      </c>
-      <c r="H28" t="str">
-        <v/>
-      </c>
-      <c r="I28" t="str">
-        <v/>
-      </c>
-      <c r="J28" t="str">
-        <v/>
-      </c>
-      <c r="K28" t="str">
-        <v/>
-      </c>
-      <c r="L28" t="str">
-        <v/>
-      </c>
-      <c r="M28" t="str">
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v>11508</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M29"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/data/monthly-revenue-11508.xlsx
+++ b/public/data/monthly-revenue-11508.xlsx
@@ -539,40 +539,40 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>樺漢</v>
+        <v>6414</v>
       </c>
       <c r="B4" t="str">
-        <v>樺漢</v>
+        <v>樺漢科技股份有限公司</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D4" t="str">
         <v>11508</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>15,486,280</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>10,825,117</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>4,661,163</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>43.06</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>117,180,186</v>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>90,560,341</v>
       </c>
       <c r="K4" t="str">
-        <v/>
+        <v>26,619,845</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>29.39</v>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -580,204 +580,204 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>瑞祺電通</v>
+        <v>6416</v>
       </c>
       <c r="B5" t="str">
-        <v>瑞祺電通</v>
+        <v>瑞祺電通股份有限公司</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D5" t="str">
         <v>11508</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>548,128</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>261,836</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>286,292</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>109.34</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>3,390,333</v>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>2,692,401</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>697,932</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>25.92</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>因應上半年部分區域訂單物料遞延，公司於階段性齊料後迅速優化生產排程並加速出貨，帶動8月單月營收成長。</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>昇貿</v>
+        <v>3305</v>
       </c>
       <c r="B6" t="str">
-        <v>昇貿</v>
+        <v>昇貿科技股份有限公司</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D6" t="str">
         <v>11508</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>1,387,596</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>941,369</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>446,227</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>47.40</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>10,786,137</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>6,680,936</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>4,105,201</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>61.45</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>價格上漲</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>慶康科技</v>
+        <v>8098</v>
       </c>
       <c r="B7" t="str">
-        <v>慶康科技</v>
+        <v>慶康科技股份有限公司</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D7" t="str">
         <v>11508</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>86,339</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>53,080</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>33,259</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>62.66</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>531,126</v>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>411,519</v>
       </c>
       <c r="K7" t="str">
-        <v/>
+        <v>119,607</v>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>29.06</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>因客戶終端需求增加，故本期營收隨之增加。</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>世紀鋼</v>
+        <v>9958</v>
       </c>
       <c r="B8" t="str">
-        <v>世紀鋼</v>
+        <v>世紀鋼鐵結構股份有限公司</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D8" t="str">
         <v>11508</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>1,804,740</v>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>944,542</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>860,198</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>91.07</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>13,917,458</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>9,836,250</v>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>4,081,208</v>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>41.49</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>本月增加百分比50%以上，主要係風力事業案依進度如期交貨及相關工程收入挹注所致。</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>騰輝電子-KY</v>
+        <v>6672</v>
       </c>
       <c r="B9" t="str">
-        <v>騰輝電子-KY</v>
+        <v>騰輝電子國際集團股份有限公司</v>
       </c>
       <c r="C9" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D9" t="str">
         <v>11508</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>805,877</v>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>345,507</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>460,370</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>133.24</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>4,330,906</v>
       </c>
       <c r="J9" t="str">
-        <v/>
+        <v>2,819,582</v>
       </c>
       <c r="K9" t="str">
-        <v/>
+        <v>1,511,324</v>
       </c>
       <c r="L9" t="str">
-        <v/>
+        <v>53.60</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -785,40 +785,40 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>中砂</v>
+        <v>1560</v>
       </c>
       <c r="B10" t="str">
-        <v>中砂</v>
+        <v>中國砂輪企業股份有限公司</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D10" t="str">
         <v>11508</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>899,115</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>689,622</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>209,493</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>30.38</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>6,571,294</v>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>5,280,144</v>
       </c>
       <c r="K10" t="str">
-        <v/>
+        <v>1,291,150</v>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>24.45</v>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -826,40 +826,40 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>耀登</v>
+        <v>3138</v>
       </c>
       <c r="B11" t="str">
-        <v>耀登</v>
+        <v>耀登科技股份有限公司</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D11" t="str">
         <v>11508</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>140,856</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>153,503</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>-12,647</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>-8.24</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>1,125,319</v>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>1,048,389</v>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>76,930</v>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>7.34</v>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -867,40 +867,40 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>材料*-KY</v>
+        <v>4763</v>
       </c>
       <c r="B12" t="str">
-        <v>材料*-KY</v>
+        <v>濟南大自然新材料股份有限公司</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D12" t="str">
         <v>11508</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>1,039,878</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>860,662</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>179,216</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>20.82</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>7,652,948</v>
       </c>
       <c r="J12" t="str">
-        <v/>
+        <v>9,676,143</v>
       </c>
       <c r="K12" t="str">
-        <v/>
+        <v>-2,023,195</v>
       </c>
       <c r="L12" t="str">
-        <v/>
+        <v>-20.91</v>
       </c>
       <c r="M12" t="str">
         <v/>
@@ -908,81 +908,81 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>晶呈科技</v>
+        <v>4768</v>
       </c>
       <c r="B13" t="str">
-        <v>晶呈科技</v>
+        <v>晶呈科技股份有限公司</v>
       </c>
       <c r="C13" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D13" t="str">
         <v>11508</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>130,197</v>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>67,419</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>62,778</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>93.12</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>1,056,471</v>
       </c>
       <c r="J13" t="str">
-        <v/>
+        <v>466,724</v>
       </c>
       <c r="K13" t="str">
-        <v/>
+        <v>589,747</v>
       </c>
       <c r="L13" t="str">
-        <v/>
+        <v>126.36</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>本月營收較去年同期增加乃因客戶需求增加</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>聖暉*</v>
+        <v>5536</v>
       </c>
       <c r="B14" t="str">
-        <v>聖暉*</v>
+        <v>聖暉工程科技股份有限公司</v>
       </c>
       <c r="C14" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D14" t="str">
         <v>11508</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>4,878,663</v>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>3,375,272</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>1,503,391</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>44.54</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>33,748,553</v>
       </c>
       <c r="J14" t="str">
-        <v/>
+        <v>26,596,497</v>
       </c>
       <c r="K14" t="str">
-        <v/>
+        <v>7,152,056</v>
       </c>
       <c r="L14" t="str">
-        <v/>
+        <v>26.89</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -990,40 +990,40 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>桓鼎-KY</v>
+        <v>5543</v>
       </c>
       <c r="B15" t="str">
-        <v>桓鼎-KY</v>
+        <v>桓鼎股份有限公司</v>
       </c>
       <c r="C15" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D15" t="str">
         <v>11508</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>227,256</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>211,978</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>15,278</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>7.21</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>2,141,825</v>
       </c>
       <c r="J15" t="str">
-        <v/>
+        <v>2,049,112</v>
       </c>
       <c r="K15" t="str">
-        <v/>
+        <v>92,713</v>
       </c>
       <c r="L15" t="str">
-        <v/>
+        <v>4.52</v>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -1031,81 +1031,81 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>朋億*</v>
+        <v>6613</v>
       </c>
       <c r="B16" t="str">
-        <v>朋億*</v>
+        <v>朋億股份有限公司</v>
       </c>
       <c r="C16" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D16" t="str">
         <v>11508</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>1,690,642</v>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>589,449</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>1,101,193</v>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>186.82</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>9,111,592</v>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>5,568,748</v>
       </c>
       <c r="K16" t="str">
-        <v/>
+        <v>3,542,844</v>
       </c>
       <c r="L16" t="str">
-        <v/>
+        <v>63.62</v>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>營收增加主係半導體廠擴廠暢旺</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>聯純</v>
+        <v>6977</v>
       </c>
       <c r="B17" t="str">
-        <v>聯純</v>
+        <v>聯純科技股份有限公司</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D17" t="str">
         <v>11508</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>196,908</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>144,562</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>52,346</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>36.21</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>1,059,087</v>
       </c>
       <c r="J17" t="str">
-        <v/>
+        <v>1,431,658</v>
       </c>
       <c r="K17" t="str">
-        <v/>
+        <v>-372,571</v>
       </c>
       <c r="L17" t="str">
-        <v/>
+        <v>-26.02</v>
       </c>
       <c r="M17" t="str">
         <v/>
@@ -1113,40 +1113,40 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>藍新資訊</v>
+        <v>6938</v>
       </c>
       <c r="B18" t="str">
-        <v>藍新資訊</v>
+        <v>藍新資訊股份有限公司</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D18" t="str">
         <v>11508</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>59,250</v>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>41,222</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>18,028</v>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>43.73</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>429,476</v>
       </c>
       <c r="J18" t="str">
-        <v/>
+        <v>340,212</v>
       </c>
       <c r="K18" t="str">
-        <v/>
+        <v>89,264</v>
       </c>
       <c r="L18" t="str">
-        <v/>
+        <v>26.24</v>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -1154,40 +1154,40 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>華勝-KY</v>
+        <v>2248</v>
       </c>
       <c r="B19" t="str">
-        <v>華勝-KY</v>
+        <v>華勝汽車電子股份有限公司</v>
       </c>
       <c r="C19" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D19" t="str">
         <v>11508</v>
       </c>
       <c r="E19" t="str">
-        <v/>
+        <v>246,526</v>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>151,780</v>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>94,746</v>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>62.42</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>1,811,034</v>
       </c>
       <c r="J19" t="str">
-        <v/>
+        <v>1,198,363</v>
       </c>
       <c r="K19" t="str">
-        <v/>
+        <v>612,671</v>
       </c>
       <c r="L19" t="str">
-        <v/>
+        <v>51.13</v>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -1195,40 +1195,40 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>樺緯物聯</v>
+        <v>7455</v>
       </c>
       <c r="B20" t="str">
-        <v>樺緯物聯</v>
+        <v>樺緯物聯股份有限公司</v>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D20" t="str">
         <v>11508</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>80,308</v>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>60,840</v>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>19,468</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>32.00</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>454,995</v>
       </c>
       <c r="J20" t="str">
-        <v/>
+        <v>575,883</v>
       </c>
       <c r="K20" t="str">
-        <v/>
+        <v>-120,888</v>
       </c>
       <c r="L20" t="str">
-        <v/>
+        <v>-20.99</v>
       </c>
       <c r="M20" t="str">
         <v/>
@@ -1236,81 +1236,81 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>達運光電</v>
+        <v>8045</v>
       </c>
       <c r="B21" t="str">
-        <v>達運光電</v>
+        <v>達運光電股份有限公司</v>
       </c>
       <c r="C21" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D21" t="str">
         <v>11508</v>
       </c>
       <c r="E21" t="str">
-        <v/>
+        <v>132,509</v>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>107,371</v>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>25,138</v>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>23.41</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>1,192,072</v>
       </c>
       <c r="J21" t="str">
-        <v/>
+        <v>892,448</v>
       </c>
       <c r="K21" t="str">
-        <v/>
+        <v>299,624</v>
       </c>
       <c r="L21" t="str">
-        <v/>
+        <v>33.57</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>產品品項增換</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>銘旺科</v>
+        <v>2429</v>
       </c>
       <c r="B22" t="str">
-        <v>銘旺科</v>
+        <v>銘旺科技股份有限公司</v>
       </c>
       <c r="C22" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D22" t="str">
         <v>11508</v>
       </c>
       <c r="E22" t="str">
-        <v/>
+        <v>28,303</v>
       </c>
       <c r="F22" t="str">
-        <v/>
+        <v>31,173</v>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>-2,870</v>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>-9.21</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>263,494</v>
       </c>
       <c r="J22" t="str">
-        <v/>
+        <v>283,424</v>
       </c>
       <c r="K22" t="str">
-        <v/>
+        <v>-19,930</v>
       </c>
       <c r="L22" t="str">
-        <v/>
+        <v>-7.03</v>
       </c>
       <c r="M22" t="str">
         <v/>
@@ -1318,81 +1318,81 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>擎亞</v>
+        <v>8096</v>
       </c>
       <c r="B23" t="str">
-        <v>擎亞</v>
+        <v>擎亞電子股份有限公司</v>
       </c>
       <c r="C23" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D23" t="str">
         <v>11508</v>
       </c>
       <c r="E23" t="str">
-        <v/>
+        <v>7,264,099</v>
       </c>
       <c r="F23" t="str">
-        <v/>
+        <v>1,965,621</v>
       </c>
       <c r="G23" t="str">
-        <v/>
+        <v>5,298,478</v>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>269.56</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>45,161,685</v>
       </c>
       <c r="J23" t="str">
-        <v/>
+        <v>24,998,502</v>
       </c>
       <c r="K23" t="str">
-        <v/>
+        <v>20,163,183</v>
       </c>
       <c r="L23" t="str">
-        <v/>
+        <v>80.66</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>因伺服器記憶體出貨量增加，致使營收較去年同期成長</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>豊漁</v>
+        <v>7847</v>
       </c>
       <c r="B24" t="str">
-        <v>豊漁</v>
+        <v>豊漁股份有限公司</v>
       </c>
       <c r="C24" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D24" t="str">
         <v>11508</v>
       </c>
       <c r="E24" t="str">
-        <v/>
+        <v>104,158</v>
       </c>
       <c r="F24" t="str">
-        <v/>
+        <v>83,839</v>
       </c>
       <c r="G24" t="str">
-        <v/>
+        <v>20,319</v>
       </c>
       <c r="H24" t="str">
-        <v/>
+        <v>24.24</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>776,959</v>
       </c>
       <c r="J24" t="str">
-        <v/>
+        <v>648,237</v>
       </c>
       <c r="K24" t="str">
-        <v/>
+        <v>128,722</v>
       </c>
       <c r="L24" t="str">
-        <v/>
+        <v>19.86</v>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -1400,40 +1400,40 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>振大環球</v>
+        <v>4441</v>
       </c>
       <c r="B25" t="str">
-        <v>振大環球</v>
+        <v>振大環球股份有限公司</v>
       </c>
       <c r="C25" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D25" t="str">
         <v>11508</v>
       </c>
       <c r="E25" t="str">
-        <v/>
+        <v>802,332</v>
       </c>
       <c r="F25" t="str">
-        <v/>
+        <v>665,511</v>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>136,821</v>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>20.56</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>5,582,634</v>
       </c>
       <c r="J25" t="str">
-        <v/>
+        <v>4,864,764</v>
       </c>
       <c r="K25" t="str">
-        <v/>
+        <v>717,870</v>
       </c>
       <c r="L25" t="str">
-        <v/>
+        <v>14.76</v>
       </c>
       <c r="M25" t="str">
         <v/>
@@ -1441,40 +1441,40 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>佐茂</v>
+        <v>7854</v>
       </c>
       <c r="B26" t="str">
-        <v>佐茂</v>
+        <v>佐茂股份有限公司</v>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D26" t="str">
         <v>11508</v>
       </c>
       <c r="E26" t="str">
-        <v/>
+        <v>180,157</v>
       </c>
       <c r="F26" t="str">
-        <v/>
+        <v>122,419</v>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>57,738</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>47.16</v>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>1,250,543</v>
       </c>
       <c r="J26" t="str">
-        <v/>
+        <v>1,090,807</v>
       </c>
       <c r="K26" t="str">
-        <v/>
+        <v>159,736</v>
       </c>
       <c r="L26" t="str">
-        <v/>
+        <v>14.64</v>
       </c>
       <c r="M26" t="str">
         <v/>
@@ -1485,40 +1485,40 @@
         <v>2330</v>
       </c>
       <c r="B27" t="str">
-        <v>2330</v>
+        <v>台灣積體電路製造股份有限公司</v>
       </c>
       <c r="C27" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D27" t="str">
         <v>11508</v>
       </c>
       <c r="E27" t="str">
-        <v/>
+        <v>514,805,337</v>
       </c>
       <c r="F27" t="str">
-        <v/>
+        <v>335,771,691</v>
       </c>
       <c r="G27" t="str">
-        <v/>
+        <v>179,033,646</v>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>53.32</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>3,386,869,575</v>
       </c>
       <c r="J27" t="str">
-        <v/>
+        <v>2,431,982,931</v>
       </c>
       <c r="K27" t="str">
-        <v/>
+        <v>954,886,644</v>
       </c>
       <c r="L27" t="str">
-        <v/>
+        <v>39.26</v>
       </c>
       <c r="M27" t="str">
-        <v/>
+        <v>因先進製程產品需求增加所致。</v>
       </c>
     </row>
     <row r="28">
@@ -1526,40 +1526,40 @@
         <v>3135</v>
       </c>
       <c r="B28" t="str">
-        <v>3135</v>
+        <v>凌航科技股份有限公司</v>
       </c>
       <c r="C28" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D28" t="str">
         <v>11508</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>1,827,285</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>540,959</v>
       </c>
       <c r="G28" t="str">
-        <v/>
+        <v>1,286,326</v>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>237.79</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>15,056,891</v>
       </c>
       <c r="J28" t="str">
-        <v/>
+        <v>4,350,127</v>
       </c>
       <c r="K28" t="str">
-        <v/>
+        <v>10,706,764</v>
       </c>
       <c r="L28" t="str">
-        <v/>
+        <v>246.13</v>
       </c>
       <c r="M28" t="str">
-        <v/>
+        <v>市場價格上漲及需求增加。</v>
       </c>
     </row>
     <row r="29">
@@ -1567,40 +1567,40 @@
         <v>8112</v>
       </c>
       <c r="B29" t="str">
-        <v>8112</v>
+        <v>至上電子股份有限公司</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D29" t="str">
         <v>11508</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>40,741,046</v>
       </c>
       <c r="F29" t="str">
-        <v/>
+        <v>15,987,240</v>
       </c>
       <c r="G29" t="str">
-        <v/>
+        <v>24,753,806</v>
       </c>
       <c r="H29" t="str">
-        <v/>
+        <v>154.83</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>378,389,981</v>
       </c>
       <c r="J29" t="str">
-        <v/>
+        <v>136,396,413</v>
       </c>
       <c r="K29" t="str">
-        <v/>
+        <v>241,993,568</v>
       </c>
       <c r="L29" t="str">
-        <v/>
+        <v>177.42</v>
       </c>
       <c r="M29" t="str">
-        <v/>
+        <v>營收大幅成長，主要係記憶體等零組件價格持續上漲，伺服器及手機客戶拉貨動能強勁所致。</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/monthly-revenue-11508.xlsx
+++ b/public/data/monthly-revenue-11508.xlsx
@@ -539,40 +539,40 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>6414</v>
+        <v>樺漢</v>
       </c>
       <c r="B4" t="str">
-        <v>樺漢科技股份有限公司</v>
+        <v>樺漢</v>
       </c>
       <c r="C4" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D4" t="str">
         <v>11508</v>
       </c>
       <c r="E4" t="str">
-        <v>15,486,280</v>
+        <v/>
       </c>
       <c r="F4" t="str">
-        <v>10,825,117</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>4,661,163</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>43.06</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>117,180,186</v>
+        <v/>
       </c>
       <c r="J4" t="str">
-        <v>90,560,341</v>
+        <v/>
       </c>
       <c r="K4" t="str">
-        <v>26,619,845</v>
+        <v/>
       </c>
       <c r="L4" t="str">
-        <v>29.39</v>
+        <v/>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -580,204 +580,204 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>6416</v>
+        <v>瑞祺電通</v>
       </c>
       <c r="B5" t="str">
-        <v>瑞祺電通股份有限公司</v>
+        <v>瑞祺電通</v>
       </c>
       <c r="C5" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D5" t="str">
         <v>11508</v>
       </c>
       <c r="E5" t="str">
-        <v>548,128</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>261,836</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>286,292</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>109.34</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>3,390,333</v>
+        <v/>
       </c>
       <c r="J5" t="str">
-        <v>2,692,401</v>
+        <v/>
       </c>
       <c r="K5" t="str">
-        <v>697,932</v>
+        <v/>
       </c>
       <c r="L5" t="str">
-        <v>25.92</v>
+        <v/>
       </c>
       <c r="M5" t="str">
-        <v>因應上半年部分區域訂單物料遞延，公司於階段性齊料後迅速優化生產排程並加速出貨，帶動8月單月營收成長。</v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3305</v>
+        <v>昇貿</v>
       </c>
       <c r="B6" t="str">
-        <v>昇貿科技股份有限公司</v>
+        <v>昇貿</v>
       </c>
       <c r="C6" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D6" t="str">
         <v>11508</v>
       </c>
       <c r="E6" t="str">
-        <v>1,387,596</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>941,369</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>446,227</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>47.40</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>10,786,137</v>
+        <v/>
       </c>
       <c r="J6" t="str">
-        <v>6,680,936</v>
+        <v/>
       </c>
       <c r="K6" t="str">
-        <v>4,105,201</v>
+        <v/>
       </c>
       <c r="L6" t="str">
-        <v>61.45</v>
+        <v/>
       </c>
       <c r="M6" t="str">
-        <v>價格上漲</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>8098</v>
+        <v>慶康科技</v>
       </c>
       <c r="B7" t="str">
-        <v>慶康科技股份有限公司</v>
+        <v>慶康科技</v>
       </c>
       <c r="C7" t="str">
-        <v>興櫃公司</v>
+        <v/>
       </c>
       <c r="D7" t="str">
         <v>11508</v>
       </c>
       <c r="E7" t="str">
-        <v>86,339</v>
+        <v/>
       </c>
       <c r="F7" t="str">
-        <v>53,080</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>33,259</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>62.66</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>531,126</v>
+        <v/>
       </c>
       <c r="J7" t="str">
-        <v>411,519</v>
+        <v/>
       </c>
       <c r="K7" t="str">
-        <v>119,607</v>
+        <v/>
       </c>
       <c r="L7" t="str">
-        <v>29.06</v>
+        <v/>
       </c>
       <c r="M7" t="str">
-        <v>因客戶終端需求增加，故本期營收隨之增加。</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>9958</v>
+        <v>世紀鋼</v>
       </c>
       <c r="B8" t="str">
-        <v>世紀鋼鐵結構股份有限公司</v>
+        <v>世紀鋼</v>
       </c>
       <c r="C8" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D8" t="str">
         <v>11508</v>
       </c>
       <c r="E8" t="str">
-        <v>1,804,740</v>
+        <v/>
       </c>
       <c r="F8" t="str">
-        <v>944,542</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>860,198</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>91.07</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>13,917,458</v>
+        <v/>
       </c>
       <c r="J8" t="str">
-        <v>9,836,250</v>
+        <v/>
       </c>
       <c r="K8" t="str">
-        <v>4,081,208</v>
+        <v/>
       </c>
       <c r="L8" t="str">
-        <v>41.49</v>
+        <v/>
       </c>
       <c r="M8" t="str">
-        <v>本月增加百分比50%以上，主要係風力事業案依進度如期交貨及相關工程收入挹注所致。</v>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>6672</v>
+        <v>騰輝電子-KY</v>
       </c>
       <c r="B9" t="str">
-        <v>騰輝電子國際集團股份有限公司</v>
+        <v>騰輝電子-KY</v>
       </c>
       <c r="C9" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D9" t="str">
         <v>11508</v>
       </c>
       <c r="E9" t="str">
-        <v>805,877</v>
+        <v/>
       </c>
       <c r="F9" t="str">
-        <v>345,507</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>460,370</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>133.24</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>4,330,906</v>
+        <v/>
       </c>
       <c r="J9" t="str">
-        <v>2,819,582</v>
+        <v/>
       </c>
       <c r="K9" t="str">
-        <v>1,511,324</v>
+        <v/>
       </c>
       <c r="L9" t="str">
-        <v>53.60</v>
+        <v/>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -785,40 +785,40 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1560</v>
+        <v>中砂</v>
       </c>
       <c r="B10" t="str">
-        <v>中國砂輪企業股份有限公司</v>
+        <v>中砂</v>
       </c>
       <c r="C10" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D10" t="str">
         <v>11508</v>
       </c>
       <c r="E10" t="str">
-        <v>899,115</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v>689,622</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>209,493</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>30.38</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>6,571,294</v>
+        <v/>
       </c>
       <c r="J10" t="str">
-        <v>5,280,144</v>
+        <v/>
       </c>
       <c r="K10" t="str">
-        <v>1,291,150</v>
+        <v/>
       </c>
       <c r="L10" t="str">
-        <v>24.45</v>
+        <v/>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -826,40 +826,40 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>3138</v>
+        <v>耀登</v>
       </c>
       <c r="B11" t="str">
-        <v>耀登科技股份有限公司</v>
+        <v>耀登</v>
       </c>
       <c r="C11" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D11" t="str">
         <v>11508</v>
       </c>
       <c r="E11" t="str">
-        <v>140,856</v>
+        <v/>
       </c>
       <c r="F11" t="str">
-        <v>153,503</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>-12,647</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>-8.24</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>1,125,319</v>
+        <v/>
       </c>
       <c r="J11" t="str">
-        <v>1,048,389</v>
+        <v/>
       </c>
       <c r="K11" t="str">
-        <v>76,930</v>
+        <v/>
       </c>
       <c r="L11" t="str">
-        <v>7.34</v>
+        <v/>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -867,40 +867,40 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>4763</v>
+        <v>材料*-KY</v>
       </c>
       <c r="B12" t="str">
-        <v>濟南大自然新材料股份有限公司</v>
+        <v>材料*-KY</v>
       </c>
       <c r="C12" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D12" t="str">
         <v>11508</v>
       </c>
       <c r="E12" t="str">
-        <v>1,039,878</v>
+        <v/>
       </c>
       <c r="F12" t="str">
-        <v>860,662</v>
+        <v/>
       </c>
       <c r="G12" t="str">
-        <v>179,216</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>20.82</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>7,652,948</v>
+        <v/>
       </c>
       <c r="J12" t="str">
-        <v>9,676,143</v>
+        <v/>
       </c>
       <c r="K12" t="str">
-        <v>-2,023,195</v>
+        <v/>
       </c>
       <c r="L12" t="str">
-        <v>-20.91</v>
+        <v/>
       </c>
       <c r="M12" t="str">
         <v/>
@@ -908,81 +908,81 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>4768</v>
+        <v>晶呈科技</v>
       </c>
       <c r="B13" t="str">
-        <v>晶呈科技股份有限公司</v>
+        <v>晶呈科技</v>
       </c>
       <c r="C13" t="str">
-        <v>上櫃公司</v>
+        <v/>
       </c>
       <c r="D13" t="str">
         <v>11508</v>
       </c>
       <c r="E13" t="str">
-        <v>130,197</v>
+        <v/>
       </c>
       <c r="F13" t="str">
-        <v>67,419</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>62,778</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v>93.12</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>1,056,471</v>
+        <v/>
       </c>
       <c r="J13" t="str">
-        <v>466,724</v>
+        <v/>
       </c>
       <c r="K13" t="str">
-        <v>589,747</v>
+        <v/>
       </c>
       <c r="L13" t="str">
-        <v>126.36</v>
+        <v/>
       </c>
       <c r="M13" t="str">
-        <v>本月營收較去年同期增加乃因客戶需求增加</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>5536</v>
+        <v>聖暉*</v>
       </c>
       <c r="B14" t="str">
-        <v>聖暉工程科技股份有限公司</v>
+        <v>聖暉*</v>
       </c>
       <c r="C14" t="str">
-        <v>上櫃公司</v>
+        <v/>
       </c>
       <c r="D14" t="str">
         <v>11508</v>
       </c>
       <c r="E14" t="str">
-        <v>4,878,663</v>
+        <v/>
       </c>
       <c r="F14" t="str">
-        <v>3,375,272</v>
+        <v/>
       </c>
       <c r="G14" t="str">
-        <v>1,503,391</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>44.54</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>33,748,553</v>
+        <v/>
       </c>
       <c r="J14" t="str">
-        <v>26,596,497</v>
+        <v/>
       </c>
       <c r="K14" t="str">
-        <v>7,152,056</v>
+        <v/>
       </c>
       <c r="L14" t="str">
-        <v>26.89</v>
+        <v/>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -990,40 +990,40 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>5543</v>
+        <v>桓鼎-KY</v>
       </c>
       <c r="B15" t="str">
-        <v>桓鼎股份有限公司</v>
+        <v>桓鼎-KY</v>
       </c>
       <c r="C15" t="str">
-        <v>上櫃公司</v>
+        <v/>
       </c>
       <c r="D15" t="str">
         <v>11508</v>
       </c>
       <c r="E15" t="str">
-        <v>227,256</v>
+        <v/>
       </c>
       <c r="F15" t="str">
-        <v>211,978</v>
+        <v/>
       </c>
       <c r="G15" t="str">
-        <v>15,278</v>
+        <v/>
       </c>
       <c r="H15" t="str">
-        <v>7.21</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>2,141,825</v>
+        <v/>
       </c>
       <c r="J15" t="str">
-        <v>2,049,112</v>
+        <v/>
       </c>
       <c r="K15" t="str">
-        <v>92,713</v>
+        <v/>
       </c>
       <c r="L15" t="str">
-        <v>4.52</v>
+        <v/>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -1031,81 +1031,81 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>6613</v>
+        <v>朋億*</v>
       </c>
       <c r="B16" t="str">
-        <v>朋億股份有限公司</v>
+        <v>朋億*</v>
       </c>
       <c r="C16" t="str">
-        <v>上櫃公司</v>
+        <v/>
       </c>
       <c r="D16" t="str">
         <v>11508</v>
       </c>
       <c r="E16" t="str">
-        <v>1,690,642</v>
+        <v/>
       </c>
       <c r="F16" t="str">
-        <v>589,449</v>
+        <v/>
       </c>
       <c r="G16" t="str">
-        <v>1,101,193</v>
+        <v/>
       </c>
       <c r="H16" t="str">
-        <v>186.82</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>9,111,592</v>
+        <v/>
       </c>
       <c r="J16" t="str">
-        <v>5,568,748</v>
+        <v/>
       </c>
       <c r="K16" t="str">
-        <v>3,542,844</v>
+        <v/>
       </c>
       <c r="L16" t="str">
-        <v>63.62</v>
+        <v/>
       </c>
       <c r="M16" t="str">
-        <v>營收增加主係半導體廠擴廠暢旺</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>6977</v>
+        <v>聯純</v>
       </c>
       <c r="B17" t="str">
-        <v>聯純科技股份有限公司</v>
+        <v>聯純</v>
       </c>
       <c r="C17" t="str">
-        <v>興櫃公司</v>
+        <v/>
       </c>
       <c r="D17" t="str">
         <v>11508</v>
       </c>
       <c r="E17" t="str">
-        <v>196,908</v>
+        <v/>
       </c>
       <c r="F17" t="str">
-        <v>144,562</v>
+        <v/>
       </c>
       <c r="G17" t="str">
-        <v>52,346</v>
+        <v/>
       </c>
       <c r="H17" t="str">
-        <v>36.21</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v>1,059,087</v>
+        <v/>
       </c>
       <c r="J17" t="str">
-        <v>1,431,658</v>
+        <v/>
       </c>
       <c r="K17" t="str">
-        <v>-372,571</v>
+        <v/>
       </c>
       <c r="L17" t="str">
-        <v>-26.02</v>
+        <v/>
       </c>
       <c r="M17" t="str">
         <v/>
@@ -1113,40 +1113,40 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>6938</v>
+        <v>藍新資訊</v>
       </c>
       <c r="B18" t="str">
-        <v>藍新資訊股份有限公司</v>
+        <v>藍新資訊</v>
       </c>
       <c r="C18" t="str">
-        <v>興櫃公司</v>
+        <v/>
       </c>
       <c r="D18" t="str">
         <v>11508</v>
       </c>
       <c r="E18" t="str">
-        <v>59,250</v>
+        <v/>
       </c>
       <c r="F18" t="str">
-        <v>41,222</v>
+        <v/>
       </c>
       <c r="G18" t="str">
-        <v>18,028</v>
+        <v/>
       </c>
       <c r="H18" t="str">
-        <v>43.73</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v>429,476</v>
+        <v/>
       </c>
       <c r="J18" t="str">
-        <v>340,212</v>
+        <v/>
       </c>
       <c r="K18" t="str">
-        <v>89,264</v>
+        <v/>
       </c>
       <c r="L18" t="str">
-        <v>26.24</v>
+        <v/>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -1154,40 +1154,40 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2248</v>
+        <v>華勝-KY</v>
       </c>
       <c r="B19" t="str">
-        <v>華勝汽車電子股份有限公司</v>
+        <v>華勝-KY</v>
       </c>
       <c r="C19" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D19" t="str">
         <v>11508</v>
       </c>
       <c r="E19" t="str">
-        <v>246,526</v>
+        <v/>
       </c>
       <c r="F19" t="str">
-        <v>151,780</v>
+        <v/>
       </c>
       <c r="G19" t="str">
-        <v>94,746</v>
+        <v/>
       </c>
       <c r="H19" t="str">
-        <v>62.42</v>
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v>1,811,034</v>
+        <v/>
       </c>
       <c r="J19" t="str">
-        <v>1,198,363</v>
+        <v/>
       </c>
       <c r="K19" t="str">
-        <v>612,671</v>
+        <v/>
       </c>
       <c r="L19" t="str">
-        <v>51.13</v>
+        <v/>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -1195,40 +1195,40 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>7455</v>
+        <v>樺緯物聯</v>
       </c>
       <c r="B20" t="str">
-        <v>樺緯物聯股份有限公司</v>
+        <v>樺緯物聯</v>
       </c>
       <c r="C20" t="str">
-        <v>興櫃公司</v>
+        <v/>
       </c>
       <c r="D20" t="str">
         <v>11508</v>
       </c>
       <c r="E20" t="str">
-        <v>80,308</v>
+        <v/>
       </c>
       <c r="F20" t="str">
-        <v>60,840</v>
+        <v/>
       </c>
       <c r="G20" t="str">
-        <v>19,468</v>
+        <v/>
       </c>
       <c r="H20" t="str">
-        <v>32.00</v>
+        <v/>
       </c>
       <c r="I20" t="str">
-        <v>454,995</v>
+        <v/>
       </c>
       <c r="J20" t="str">
-        <v>575,883</v>
+        <v/>
       </c>
       <c r="K20" t="str">
-        <v>-120,888</v>
+        <v/>
       </c>
       <c r="L20" t="str">
-        <v>-20.99</v>
+        <v/>
       </c>
       <c r="M20" t="str">
         <v/>
@@ -1236,81 +1236,81 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>8045</v>
+        <v>達運光電</v>
       </c>
       <c r="B21" t="str">
-        <v>達運光電股份有限公司</v>
+        <v>達運光電</v>
       </c>
       <c r="C21" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D21" t="str">
         <v>11508</v>
       </c>
       <c r="E21" t="str">
-        <v>132,509</v>
+        <v/>
       </c>
       <c r="F21" t="str">
-        <v>107,371</v>
+        <v/>
       </c>
       <c r="G21" t="str">
-        <v>25,138</v>
+        <v/>
       </c>
       <c r="H21" t="str">
-        <v>23.41</v>
+        <v/>
       </c>
       <c r="I21" t="str">
-        <v>1,192,072</v>
+        <v/>
       </c>
       <c r="J21" t="str">
-        <v>892,448</v>
+        <v/>
       </c>
       <c r="K21" t="str">
-        <v>299,624</v>
+        <v/>
       </c>
       <c r="L21" t="str">
-        <v>33.57</v>
+        <v/>
       </c>
       <c r="M21" t="str">
-        <v>產品品項增換</v>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2429</v>
+        <v>銘旺科</v>
       </c>
       <c r="B22" t="str">
-        <v>銘旺科技股份有限公司</v>
+        <v>銘旺科</v>
       </c>
       <c r="C22" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D22" t="str">
         <v>11508</v>
       </c>
       <c r="E22" t="str">
-        <v>28,303</v>
+        <v/>
       </c>
       <c r="F22" t="str">
-        <v>31,173</v>
+        <v/>
       </c>
       <c r="G22" t="str">
-        <v>-2,870</v>
+        <v/>
       </c>
       <c r="H22" t="str">
-        <v>-9.21</v>
+        <v/>
       </c>
       <c r="I22" t="str">
-        <v>263,494</v>
+        <v/>
       </c>
       <c r="J22" t="str">
-        <v>283,424</v>
+        <v/>
       </c>
       <c r="K22" t="str">
-        <v>-19,930</v>
+        <v/>
       </c>
       <c r="L22" t="str">
-        <v>-7.03</v>
+        <v/>
       </c>
       <c r="M22" t="str">
         <v/>
@@ -1318,81 +1318,81 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>8096</v>
+        <v>擎亞</v>
       </c>
       <c r="B23" t="str">
-        <v>擎亞電子股份有限公司</v>
+        <v>擎亞</v>
       </c>
       <c r="C23" t="str">
-        <v>上櫃公司</v>
+        <v/>
       </c>
       <c r="D23" t="str">
         <v>11508</v>
       </c>
       <c r="E23" t="str">
-        <v>7,264,099</v>
+        <v/>
       </c>
       <c r="F23" t="str">
-        <v>1,965,621</v>
+        <v/>
       </c>
       <c r="G23" t="str">
-        <v>5,298,478</v>
+        <v/>
       </c>
       <c r="H23" t="str">
-        <v>269.56</v>
+        <v/>
       </c>
       <c r="I23" t="str">
-        <v>45,161,685</v>
+        <v/>
       </c>
       <c r="J23" t="str">
-        <v>24,998,502</v>
+        <v/>
       </c>
       <c r="K23" t="str">
-        <v>20,163,183</v>
+        <v/>
       </c>
       <c r="L23" t="str">
-        <v>80.66</v>
+        <v/>
       </c>
       <c r="M23" t="str">
-        <v>因伺服器記憶體出貨量增加，致使營收較去年同期成長</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>7847</v>
+        <v>豊漁</v>
       </c>
       <c r="B24" t="str">
-        <v>豊漁股份有限公司</v>
+        <v>豊漁</v>
       </c>
       <c r="C24" t="str">
-        <v>興櫃公司</v>
+        <v/>
       </c>
       <c r="D24" t="str">
         <v>11508</v>
       </c>
       <c r="E24" t="str">
-        <v>104,158</v>
+        <v/>
       </c>
       <c r="F24" t="str">
-        <v>83,839</v>
+        <v/>
       </c>
       <c r="G24" t="str">
-        <v>20,319</v>
+        <v/>
       </c>
       <c r="H24" t="str">
-        <v>24.24</v>
+        <v/>
       </c>
       <c r="I24" t="str">
-        <v>776,959</v>
+        <v/>
       </c>
       <c r="J24" t="str">
-        <v>648,237</v>
+        <v/>
       </c>
       <c r="K24" t="str">
-        <v>128,722</v>
+        <v/>
       </c>
       <c r="L24" t="str">
-        <v>19.86</v>
+        <v/>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -1400,40 +1400,40 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>4441</v>
+        <v>振大環球</v>
       </c>
       <c r="B25" t="str">
-        <v>振大環球股份有限公司</v>
+        <v>振大環球</v>
       </c>
       <c r="C25" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D25" t="str">
         <v>11508</v>
       </c>
       <c r="E25" t="str">
-        <v>802,332</v>
+        <v/>
       </c>
       <c r="F25" t="str">
-        <v>665,511</v>
+        <v/>
       </c>
       <c r="G25" t="str">
-        <v>136,821</v>
+        <v/>
       </c>
       <c r="H25" t="str">
-        <v>20.56</v>
+        <v/>
       </c>
       <c r="I25" t="str">
-        <v>5,582,634</v>
+        <v/>
       </c>
       <c r="J25" t="str">
-        <v>4,864,764</v>
+        <v/>
       </c>
       <c r="K25" t="str">
-        <v>717,870</v>
+        <v/>
       </c>
       <c r="L25" t="str">
-        <v>14.76</v>
+        <v/>
       </c>
       <c r="M25" t="str">
         <v/>
@@ -1441,40 +1441,40 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>7854</v>
+        <v>佐茂</v>
       </c>
       <c r="B26" t="str">
-        <v>佐茂股份有限公司</v>
+        <v>佐茂</v>
       </c>
       <c r="C26" t="str">
-        <v>興櫃公司</v>
+        <v/>
       </c>
       <c r="D26" t="str">
         <v>11508</v>
       </c>
       <c r="E26" t="str">
-        <v>180,157</v>
+        <v/>
       </c>
       <c r="F26" t="str">
-        <v>122,419</v>
+        <v/>
       </c>
       <c r="G26" t="str">
-        <v>57,738</v>
+        <v/>
       </c>
       <c r="H26" t="str">
-        <v>47.16</v>
+        <v/>
       </c>
       <c r="I26" t="str">
-        <v>1,250,543</v>
+        <v/>
       </c>
       <c r="J26" t="str">
-        <v>1,090,807</v>
+        <v/>
       </c>
       <c r="K26" t="str">
-        <v>159,736</v>
+        <v/>
       </c>
       <c r="L26" t="str">
-        <v>14.64</v>
+        <v/>
       </c>
       <c r="M26" t="str">
         <v/>
@@ -1485,40 +1485,40 @@
         <v>2330</v>
       </c>
       <c r="B27" t="str">
-        <v>台灣積體電路製造股份有限公司</v>
+        <v>2330</v>
       </c>
       <c r="C27" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D27" t="str">
         <v>11508</v>
       </c>
       <c r="E27" t="str">
-        <v>514,805,337</v>
+        <v/>
       </c>
       <c r="F27" t="str">
-        <v>335,771,691</v>
+        <v/>
       </c>
       <c r="G27" t="str">
-        <v>179,033,646</v>
+        <v/>
       </c>
       <c r="H27" t="str">
-        <v>53.32</v>
+        <v/>
       </c>
       <c r="I27" t="str">
-        <v>3,386,869,575</v>
+        <v/>
       </c>
       <c r="J27" t="str">
-        <v>2,431,982,931</v>
+        <v/>
       </c>
       <c r="K27" t="str">
-        <v>954,886,644</v>
+        <v/>
       </c>
       <c r="L27" t="str">
-        <v>39.26</v>
+        <v/>
       </c>
       <c r="M27" t="str">
-        <v>因先進製程產品需求增加所致。</v>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -1526,40 +1526,40 @@
         <v>3135</v>
       </c>
       <c r="B28" t="str">
-        <v>凌航科技股份有限公司</v>
+        <v>3135</v>
       </c>
       <c r="C28" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D28" t="str">
         <v>11508</v>
       </c>
       <c r="E28" t="str">
-        <v>1,827,285</v>
+        <v/>
       </c>
       <c r="F28" t="str">
-        <v>540,959</v>
+        <v/>
       </c>
       <c r="G28" t="str">
-        <v>1,286,326</v>
+        <v/>
       </c>
       <c r="H28" t="str">
-        <v>237.79</v>
+        <v/>
       </c>
       <c r="I28" t="str">
-        <v>15,056,891</v>
+        <v/>
       </c>
       <c r="J28" t="str">
-        <v>4,350,127</v>
+        <v/>
       </c>
       <c r="K28" t="str">
-        <v>10,706,764</v>
+        <v/>
       </c>
       <c r="L28" t="str">
-        <v>246.13</v>
+        <v/>
       </c>
       <c r="M28" t="str">
-        <v>市場價格上漲及需求增加。</v>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1567,40 +1567,40 @@
         <v>8112</v>
       </c>
       <c r="B29" t="str">
-        <v>至上電子股份有限公司</v>
+        <v>8112</v>
       </c>
       <c r="C29" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D29" t="str">
         <v>11508</v>
       </c>
       <c r="E29" t="str">
-        <v>40,741,046</v>
+        <v/>
       </c>
       <c r="F29" t="str">
-        <v>15,987,240</v>
+        <v/>
       </c>
       <c r="G29" t="str">
-        <v>24,753,806</v>
+        <v/>
       </c>
       <c r="H29" t="str">
-        <v>154.83</v>
+        <v/>
       </c>
       <c r="I29" t="str">
-        <v>378,389,981</v>
+        <v/>
       </c>
       <c r="J29" t="str">
-        <v>136,396,413</v>
+        <v/>
       </c>
       <c r="K29" t="str">
-        <v>241,993,568</v>
+        <v/>
       </c>
       <c r="L29" t="str">
-        <v>177.42</v>
+        <v/>
       </c>
       <c r="M29" t="str">
-        <v>營收大幅成長，主要係記憶體等零組件價格持續上漲，伺服器及手機客戶拉貨動能強勁所致。</v>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/public/data/monthly-revenue-11508.xlsx
+++ b/public/data/monthly-revenue-11508.xlsx
@@ -457,40 +457,40 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>友威科</v>
+        <v>3580</v>
       </c>
       <c r="B2" t="str">
-        <v>友威科</v>
+        <v>友威科技股份有限公司</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D2" t="str">
         <v>11508</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>46,361</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>36,545</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>9,816</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>26.86</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>265,591</v>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>282,548</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>-16,957</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>-6.00</v>
       </c>
       <c r="M2" t="str">
         <v/>
@@ -498,40 +498,40 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>德微</v>
+        <v>3675</v>
       </c>
       <c r="B3" t="str">
-        <v>德微</v>
+        <v>德微科技股份有限公司</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D3" t="str">
         <v>11508</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>300,057</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>228,170</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>71,887</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>31.51</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>2,076,632</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>1,720,901</v>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>355,731</v>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>20.67</v>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -539,40 +539,40 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>樺漢</v>
+        <v>6414</v>
       </c>
       <c r="B4" t="str">
-        <v>樺漢</v>
+        <v>樺漢科技股份有限公司</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D4" t="str">
         <v>11508</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>15,486,280</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>10,825,117</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>4,661,163</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>43.06</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>117,180,186</v>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>90,560,341</v>
       </c>
       <c r="K4" t="str">
-        <v/>
+        <v>26,619,845</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>29.39</v>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -580,204 +580,204 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>瑞祺電通</v>
+        <v>6416</v>
       </c>
       <c r="B5" t="str">
-        <v>瑞祺電通</v>
+        <v>瑞祺電通股份有限公司</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D5" t="str">
         <v>11508</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>548,128</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>261,836</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>286,292</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>109.34</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>3,390,333</v>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>2,692,401</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>697,932</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>25.92</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>因應上半年部分區域訂單物料遞延，公司於階段性齊料後迅速優化生產排程並加速出貨，帶動8月單月營收成長。</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>昇貿</v>
+        <v>3305</v>
       </c>
       <c r="B6" t="str">
-        <v>昇貿</v>
+        <v>昇貿科技股份有限公司</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D6" t="str">
         <v>11508</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>1,387,596</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>941,369</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>446,227</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>47.40</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>10,786,137</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>6,680,936</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>4,105,201</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>61.45</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>價格上漲</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>慶康科技</v>
+        <v>8098</v>
       </c>
       <c r="B7" t="str">
-        <v>慶康科技</v>
+        <v>慶康科技股份有限公司</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D7" t="str">
         <v>11508</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>86,339</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>53,080</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>33,259</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>62.66</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>531,126</v>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>411,519</v>
       </c>
       <c r="K7" t="str">
-        <v/>
+        <v>119,607</v>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>29.06</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>因客戶終端需求增加，故本期營收隨之增加。</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>世紀鋼</v>
+        <v>9958</v>
       </c>
       <c r="B8" t="str">
-        <v>世紀鋼</v>
+        <v>世紀鋼鐵結構股份有限公司</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D8" t="str">
         <v>11508</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>1,804,740</v>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>944,542</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>860,198</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>91.07</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>13,917,458</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>9,836,250</v>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>4,081,208</v>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>41.49</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>本月增加百分比50%以上，主要係風力事業案依進度如期交貨及相關工程收入挹注所致。</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>騰輝電子-KY</v>
+        <v>6672</v>
       </c>
       <c r="B9" t="str">
-        <v>騰輝電子-KY</v>
+        <v>騰輝電子國際集團股份有限公司</v>
       </c>
       <c r="C9" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D9" t="str">
         <v>11508</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>805,877</v>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>345,507</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>460,370</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>133.24</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>4,330,906</v>
       </c>
       <c r="J9" t="str">
-        <v/>
+        <v>2,819,582</v>
       </c>
       <c r="K9" t="str">
-        <v/>
+        <v>1,511,324</v>
       </c>
       <c r="L9" t="str">
-        <v/>
+        <v>53.60</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -785,40 +785,40 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>中砂</v>
+        <v>1560</v>
       </c>
       <c r="B10" t="str">
-        <v>中砂</v>
+        <v>中國砂輪企業股份有限公司</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D10" t="str">
         <v>11508</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>899,115</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>689,622</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>209,493</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>30.38</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>6,571,294</v>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>5,280,144</v>
       </c>
       <c r="K10" t="str">
-        <v/>
+        <v>1,291,150</v>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>24.45</v>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -826,40 +826,40 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>耀登</v>
+        <v>3138</v>
       </c>
       <c r="B11" t="str">
-        <v>耀登</v>
+        <v>耀登科技股份有限公司</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D11" t="str">
         <v>11508</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>140,856</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>153,503</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>-12,647</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>-8.24</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>1,125,319</v>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>1,048,389</v>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>76,930</v>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>7.34</v>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -867,40 +867,40 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>材料*-KY</v>
+        <v>4763</v>
       </c>
       <c r="B12" t="str">
-        <v>材料*-KY</v>
+        <v>濟南大自然新材料股份有限公司</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D12" t="str">
         <v>11508</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>1,039,878</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>860,662</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>179,216</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>20.82</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>7,652,948</v>
       </c>
       <c r="J12" t="str">
-        <v/>
+        <v>9,676,143</v>
       </c>
       <c r="K12" t="str">
-        <v/>
+        <v>-2,023,195</v>
       </c>
       <c r="L12" t="str">
-        <v/>
+        <v>-20.91</v>
       </c>
       <c r="M12" t="str">
         <v/>
@@ -908,81 +908,81 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>晶呈科技</v>
+        <v>4768</v>
       </c>
       <c r="B13" t="str">
-        <v>晶呈科技</v>
+        <v>晶呈科技股份有限公司</v>
       </c>
       <c r="C13" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D13" t="str">
         <v>11508</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>130,197</v>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>67,419</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>62,778</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>93.12</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>1,056,471</v>
       </c>
       <c r="J13" t="str">
-        <v/>
+        <v>466,724</v>
       </c>
       <c r="K13" t="str">
-        <v/>
+        <v>589,747</v>
       </c>
       <c r="L13" t="str">
-        <v/>
+        <v>126.36</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>本月營收較去年同期增加乃因客戶需求增加</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>聖暉*</v>
+        <v>5536</v>
       </c>
       <c r="B14" t="str">
-        <v>聖暉*</v>
+        <v>聖暉工程科技股份有限公司</v>
       </c>
       <c r="C14" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D14" t="str">
         <v>11508</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>4,878,663</v>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>3,375,272</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>1,503,391</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>44.54</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>33,748,553</v>
       </c>
       <c r="J14" t="str">
-        <v/>
+        <v>26,596,497</v>
       </c>
       <c r="K14" t="str">
-        <v/>
+        <v>7,152,056</v>
       </c>
       <c r="L14" t="str">
-        <v/>
+        <v>26.89</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -990,40 +990,40 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>桓鼎-KY</v>
+        <v>5543</v>
       </c>
       <c r="B15" t="str">
-        <v>桓鼎-KY</v>
+        <v>桓鼎股份有限公司</v>
       </c>
       <c r="C15" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D15" t="str">
         <v>11508</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>227,256</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>211,978</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>15,278</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>7.21</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>2,141,825</v>
       </c>
       <c r="J15" t="str">
-        <v/>
+        <v>2,049,112</v>
       </c>
       <c r="K15" t="str">
-        <v/>
+        <v>92,713</v>
       </c>
       <c r="L15" t="str">
-        <v/>
+        <v>4.52</v>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -1031,81 +1031,81 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>朋億*</v>
+        <v>6613</v>
       </c>
       <c r="B16" t="str">
-        <v>朋億*</v>
+        <v>朋億股份有限公司</v>
       </c>
       <c r="C16" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D16" t="str">
         <v>11508</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>1,690,642</v>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>589,449</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>1,101,193</v>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>186.82</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>9,111,592</v>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>5,568,748</v>
       </c>
       <c r="K16" t="str">
-        <v/>
+        <v>3,542,844</v>
       </c>
       <c r="L16" t="str">
-        <v/>
+        <v>63.62</v>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>營收增加主係半導體廠擴廠暢旺</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>聯純</v>
+        <v>6977</v>
       </c>
       <c r="B17" t="str">
-        <v>聯純</v>
+        <v>聯純科技股份有限公司</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D17" t="str">
         <v>11508</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>196,908</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>144,562</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>52,346</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>36.21</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>1,059,087</v>
       </c>
       <c r="J17" t="str">
-        <v/>
+        <v>1,431,658</v>
       </c>
       <c r="K17" t="str">
-        <v/>
+        <v>-372,571</v>
       </c>
       <c r="L17" t="str">
-        <v/>
+        <v>-26.02</v>
       </c>
       <c r="M17" t="str">
         <v/>
@@ -1113,40 +1113,40 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>藍新資訊</v>
+        <v>6938</v>
       </c>
       <c r="B18" t="str">
-        <v>藍新資訊</v>
+        <v>藍新資訊股份有限公司</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D18" t="str">
         <v>11508</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>59,250</v>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>41,222</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>18,028</v>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>43.73</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>429,476</v>
       </c>
       <c r="J18" t="str">
-        <v/>
+        <v>340,212</v>
       </c>
       <c r="K18" t="str">
-        <v/>
+        <v>89,264</v>
       </c>
       <c r="L18" t="str">
-        <v/>
+        <v>26.24</v>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -1154,40 +1154,40 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>華勝-KY</v>
+        <v>2248</v>
       </c>
       <c r="B19" t="str">
-        <v>華勝-KY</v>
+        <v>華勝汽車電子股份有限公司</v>
       </c>
       <c r="C19" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D19" t="str">
         <v>11508</v>
       </c>
       <c r="E19" t="str">
-        <v/>
+        <v>246,526</v>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>151,780</v>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>94,746</v>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>62.42</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>1,811,034</v>
       </c>
       <c r="J19" t="str">
-        <v/>
+        <v>1,198,363</v>
       </c>
       <c r="K19" t="str">
-        <v/>
+        <v>612,671</v>
       </c>
       <c r="L19" t="str">
-        <v/>
+        <v>51.13</v>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -1195,40 +1195,40 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>樺緯物聯</v>
+        <v>7455</v>
       </c>
       <c r="B20" t="str">
-        <v>樺緯物聯</v>
+        <v>樺緯物聯股份有限公司</v>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D20" t="str">
         <v>11508</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>80,308</v>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>60,840</v>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>19,468</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>32.00</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>454,995</v>
       </c>
       <c r="J20" t="str">
-        <v/>
+        <v>575,883</v>
       </c>
       <c r="K20" t="str">
-        <v/>
+        <v>-120,888</v>
       </c>
       <c r="L20" t="str">
-        <v/>
+        <v>-20.99</v>
       </c>
       <c r="M20" t="str">
         <v/>
@@ -1236,81 +1236,81 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>達運光電</v>
+        <v>8045</v>
       </c>
       <c r="B21" t="str">
-        <v>達運光電</v>
+        <v>達運光電股份有限公司</v>
       </c>
       <c r="C21" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D21" t="str">
         <v>11508</v>
       </c>
       <c r="E21" t="str">
-        <v/>
+        <v>132,509</v>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>107,371</v>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>25,138</v>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>23.41</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>1,192,072</v>
       </c>
       <c r="J21" t="str">
-        <v/>
+        <v>892,448</v>
       </c>
       <c r="K21" t="str">
-        <v/>
+        <v>299,624</v>
       </c>
       <c r="L21" t="str">
-        <v/>
+        <v>33.57</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>產品品項增換</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>銘旺科</v>
+        <v>2429</v>
       </c>
       <c r="B22" t="str">
-        <v>銘旺科</v>
+        <v>銘旺科技股份有限公司</v>
       </c>
       <c r="C22" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D22" t="str">
         <v>11508</v>
       </c>
       <c r="E22" t="str">
-        <v/>
+        <v>28,303</v>
       </c>
       <c r="F22" t="str">
-        <v/>
+        <v>31,173</v>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>-2,870</v>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>-9.21</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>263,494</v>
       </c>
       <c r="J22" t="str">
-        <v/>
+        <v>283,424</v>
       </c>
       <c r="K22" t="str">
-        <v/>
+        <v>-19,930</v>
       </c>
       <c r="L22" t="str">
-        <v/>
+        <v>-7.03</v>
       </c>
       <c r="M22" t="str">
         <v/>
@@ -1318,81 +1318,81 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>擎亞</v>
+        <v>8096</v>
       </c>
       <c r="B23" t="str">
-        <v>擎亞</v>
+        <v>擎亞電子股份有限公司</v>
       </c>
       <c r="C23" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D23" t="str">
         <v>11508</v>
       </c>
       <c r="E23" t="str">
-        <v/>
+        <v>7,264,099</v>
       </c>
       <c r="F23" t="str">
-        <v/>
+        <v>1,965,621</v>
       </c>
       <c r="G23" t="str">
-        <v/>
+        <v>5,298,478</v>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>269.56</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>45,161,685</v>
       </c>
       <c r="J23" t="str">
-        <v/>
+        <v>24,998,502</v>
       </c>
       <c r="K23" t="str">
-        <v/>
+        <v>20,163,183</v>
       </c>
       <c r="L23" t="str">
-        <v/>
+        <v>80.66</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>因伺服器記憶體出貨量增加，致使營收較去年同期成長</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>豊漁</v>
+        <v>7847</v>
       </c>
       <c r="B24" t="str">
-        <v>豊漁</v>
+        <v>豊漁股份有限公司</v>
       </c>
       <c r="C24" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D24" t="str">
         <v>11508</v>
       </c>
       <c r="E24" t="str">
-        <v/>
+        <v>104,158</v>
       </c>
       <c r="F24" t="str">
-        <v/>
+        <v>83,839</v>
       </c>
       <c r="G24" t="str">
-        <v/>
+        <v>20,319</v>
       </c>
       <c r="H24" t="str">
-        <v/>
+        <v>24.24</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>776,959</v>
       </c>
       <c r="J24" t="str">
-        <v/>
+        <v>648,237</v>
       </c>
       <c r="K24" t="str">
-        <v/>
+        <v>128,722</v>
       </c>
       <c r="L24" t="str">
-        <v/>
+        <v>19.86</v>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -1400,40 +1400,40 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>振大環球</v>
+        <v>4441</v>
       </c>
       <c r="B25" t="str">
-        <v>振大環球</v>
+        <v>振大環球股份有限公司</v>
       </c>
       <c r="C25" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D25" t="str">
         <v>11508</v>
       </c>
       <c r="E25" t="str">
-        <v/>
+        <v>802,332</v>
       </c>
       <c r="F25" t="str">
-        <v/>
+        <v>665,511</v>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>136,821</v>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>20.56</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>5,582,634</v>
       </c>
       <c r="J25" t="str">
-        <v/>
+        <v>4,864,764</v>
       </c>
       <c r="K25" t="str">
-        <v/>
+        <v>717,870</v>
       </c>
       <c r="L25" t="str">
-        <v/>
+        <v>14.76</v>
       </c>
       <c r="M25" t="str">
         <v/>
@@ -1441,40 +1441,40 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>佐茂</v>
+        <v>7854</v>
       </c>
       <c r="B26" t="str">
-        <v>佐茂</v>
+        <v>佐茂股份有限公司</v>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D26" t="str">
         <v>11508</v>
       </c>
       <c r="E26" t="str">
-        <v/>
+        <v>180,157</v>
       </c>
       <c r="F26" t="str">
-        <v/>
+        <v>122,419</v>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>57,738</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>47.16</v>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>1,250,543</v>
       </c>
       <c r="J26" t="str">
-        <v/>
+        <v>1,090,807</v>
       </c>
       <c r="K26" t="str">
-        <v/>
+        <v>159,736</v>
       </c>
       <c r="L26" t="str">
-        <v/>
+        <v>14.64</v>
       </c>
       <c r="M26" t="str">
         <v/>
@@ -1485,40 +1485,40 @@
         <v>2330</v>
       </c>
       <c r="B27" t="str">
-        <v>2330</v>
+        <v>台灣積體電路製造股份有限公司</v>
       </c>
       <c r="C27" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D27" t="str">
         <v>11508</v>
       </c>
       <c r="E27" t="str">
-        <v/>
+        <v>514,805,337</v>
       </c>
       <c r="F27" t="str">
-        <v/>
+        <v>335,771,691</v>
       </c>
       <c r="G27" t="str">
-        <v/>
+        <v>179,033,646</v>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>53.32</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>3,386,869,575</v>
       </c>
       <c r="J27" t="str">
-        <v/>
+        <v>2,431,982,931</v>
       </c>
       <c r="K27" t="str">
-        <v/>
+        <v>954,886,644</v>
       </c>
       <c r="L27" t="str">
-        <v/>
+        <v>39.26</v>
       </c>
       <c r="M27" t="str">
-        <v/>
+        <v>因先進製程產品需求增加所致。</v>
       </c>
     </row>
     <row r="28">
@@ -1526,40 +1526,40 @@
         <v>3135</v>
       </c>
       <c r="B28" t="str">
-        <v>3135</v>
+        <v>凌航科技股份有限公司</v>
       </c>
       <c r="C28" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D28" t="str">
         <v>11508</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>1,827,285</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>540,959</v>
       </c>
       <c r="G28" t="str">
-        <v/>
+        <v>1,286,326</v>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>237.79</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>15,056,891</v>
       </c>
       <c r="J28" t="str">
-        <v/>
+        <v>4,350,127</v>
       </c>
       <c r="K28" t="str">
-        <v/>
+        <v>10,706,764</v>
       </c>
       <c r="L28" t="str">
-        <v/>
+        <v>246.13</v>
       </c>
       <c r="M28" t="str">
-        <v/>
+        <v>市場價格上漲及需求增加。</v>
       </c>
     </row>
     <row r="29">
@@ -1567,40 +1567,40 @@
         <v>8112</v>
       </c>
       <c r="B29" t="str">
-        <v>8112</v>
+        <v>至上電子股份有限公司</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D29" t="str">
         <v>11508</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>40,741,046</v>
       </c>
       <c r="F29" t="str">
-        <v/>
+        <v>15,987,240</v>
       </c>
       <c r="G29" t="str">
-        <v/>
+        <v>24,753,806</v>
       </c>
       <c r="H29" t="str">
-        <v/>
+        <v>154.83</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>378,389,981</v>
       </c>
       <c r="J29" t="str">
-        <v/>
+        <v>136,396,413</v>
       </c>
       <c r="K29" t="str">
-        <v/>
+        <v>241,993,568</v>
       </c>
       <c r="L29" t="str">
-        <v/>
+        <v>177.42</v>
       </c>
       <c r="M29" t="str">
-        <v/>
+        <v>營收大幅成長，主要係記憶體等零組件價格持續上漲，伺服器及手機客戶拉貨動能強勁所致。</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/monthly-revenue-11508.xlsx
+++ b/public/data/monthly-revenue-11508.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M28"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -460,7 +460,7 @@
         <v>3580</v>
       </c>
       <c r="B2" t="str">
-        <v>友威科技股份有限公司</v>
+        <v>友威科</v>
       </c>
       <c r="C2" t="str">
         <v>上櫃公司</v>
@@ -501,7 +501,7 @@
         <v>3675</v>
       </c>
       <c r="B3" t="str">
-        <v>德微科技股份有限公司</v>
+        <v>德微</v>
       </c>
       <c r="C3" t="str">
         <v>上櫃公司</v>
@@ -542,7 +542,7 @@
         <v>6414</v>
       </c>
       <c r="B4" t="str">
-        <v>樺漢科技股份有限公司</v>
+        <v>樺漢</v>
       </c>
       <c r="C4" t="str">
         <v>上市公司</v>
@@ -583,7 +583,7 @@
         <v>6416</v>
       </c>
       <c r="B5" t="str">
-        <v>瑞祺電通股份有限公司</v>
+        <v>瑞祺電通</v>
       </c>
       <c r="C5" t="str">
         <v>上市公司</v>
@@ -624,7 +624,7 @@
         <v>3305</v>
       </c>
       <c r="B6" t="str">
-        <v>昇貿科技股份有限公司</v>
+        <v>昇貿</v>
       </c>
       <c r="C6" t="str">
         <v>上市公司</v>
@@ -665,7 +665,7 @@
         <v>8098</v>
       </c>
       <c r="B7" t="str">
-        <v>慶康科技股份有限公司</v>
+        <v>慶康科技</v>
       </c>
       <c r="C7" t="str">
         <v>興櫃公司</v>
@@ -706,7 +706,7 @@
         <v>9958</v>
       </c>
       <c r="B8" t="str">
-        <v>世紀鋼鐵結構股份有限公司</v>
+        <v>世紀鋼</v>
       </c>
       <c r="C8" t="str">
         <v>上市公司</v>
@@ -747,7 +747,7 @@
         <v>6672</v>
       </c>
       <c r="B9" t="str">
-        <v>騰輝電子國際集團股份有限公司</v>
+        <v>騰輝電子-KY</v>
       </c>
       <c r="C9" t="str">
         <v>上市公司</v>
@@ -788,7 +788,7 @@
         <v>1560</v>
       </c>
       <c r="B10" t="str">
-        <v>中國砂輪企業股份有限公司</v>
+        <v>中砂</v>
       </c>
       <c r="C10" t="str">
         <v>上市公司</v>
@@ -829,7 +829,7 @@
         <v>3138</v>
       </c>
       <c r="B11" t="str">
-        <v>耀登科技股份有限公司</v>
+        <v>耀登</v>
       </c>
       <c r="C11" t="str">
         <v>上市公司</v>
@@ -867,51 +867,51 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>4763</v>
+        <v>4768</v>
       </c>
       <c r="B12" t="str">
-        <v>濟南大自然新材料股份有限公司</v>
+        <v>晶呈科技</v>
       </c>
       <c r="C12" t="str">
-        <v>上市公司</v>
+        <v>上櫃公司</v>
       </c>
       <c r="D12" t="str">
         <v>11508</v>
       </c>
       <c r="E12" t="str">
-        <v>1,039,878</v>
+        <v>130,197</v>
       </c>
       <c r="F12" t="str">
-        <v>860,662</v>
+        <v>67,419</v>
       </c>
       <c r="G12" t="str">
-        <v>179,216</v>
+        <v>62,778</v>
       </c>
       <c r="H12" t="str">
-        <v>20.82</v>
+        <v>93.12</v>
       </c>
       <c r="I12" t="str">
-        <v>7,652,948</v>
+        <v>1,056,471</v>
       </c>
       <c r="J12" t="str">
-        <v>9,676,143</v>
+        <v>466,724</v>
       </c>
       <c r="K12" t="str">
-        <v>-2,023,195</v>
+        <v>589,747</v>
       </c>
       <c r="L12" t="str">
-        <v>-20.91</v>
+        <v>126.36</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>本月營收較去年同期增加乃因客戶需求增加</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>4768</v>
+        <v>5536</v>
       </c>
       <c r="B13" t="str">
-        <v>晶呈科技股份有限公司</v>
+        <v>聖暉*</v>
       </c>
       <c r="C13" t="str">
         <v>上櫃公司</v>
@@ -920,39 +920,39 @@
         <v>11508</v>
       </c>
       <c r="E13" t="str">
-        <v>130,197</v>
+        <v>4,878,663</v>
       </c>
       <c r="F13" t="str">
-        <v>67,419</v>
+        <v>3,375,272</v>
       </c>
       <c r="G13" t="str">
-        <v>62,778</v>
+        <v>1,503,391</v>
       </c>
       <c r="H13" t="str">
-        <v>93.12</v>
+        <v>44.54</v>
       </c>
       <c r="I13" t="str">
-        <v>1,056,471</v>
+        <v>33,748,553</v>
       </c>
       <c r="J13" t="str">
-        <v>466,724</v>
+        <v>26,596,497</v>
       </c>
       <c r="K13" t="str">
-        <v>589,747</v>
+        <v>7,152,056</v>
       </c>
       <c r="L13" t="str">
-        <v>126.36</v>
+        <v>26.89</v>
       </c>
       <c r="M13" t="str">
-        <v>本月營收較去年同期增加乃因客戶需求增加</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>5536</v>
+        <v>5543</v>
       </c>
       <c r="B14" t="str">
-        <v>聖暉工程科技股份有限公司</v>
+        <v>桓鼎-KY</v>
       </c>
       <c r="C14" t="str">
         <v>上櫃公司</v>
@@ -961,28 +961,28 @@
         <v>11508</v>
       </c>
       <c r="E14" t="str">
-        <v>4,878,663</v>
+        <v>227,256</v>
       </c>
       <c r="F14" t="str">
-        <v>3,375,272</v>
+        <v>211,978</v>
       </c>
       <c r="G14" t="str">
-        <v>1,503,391</v>
+        <v>15,278</v>
       </c>
       <c r="H14" t="str">
-        <v>44.54</v>
+        <v>7.21</v>
       </c>
       <c r="I14" t="str">
-        <v>33,748,553</v>
+        <v>2,141,825</v>
       </c>
       <c r="J14" t="str">
-        <v>26,596,497</v>
+        <v>2,049,112</v>
       </c>
       <c r="K14" t="str">
-        <v>7,152,056</v>
+        <v>92,713</v>
       </c>
       <c r="L14" t="str">
-        <v>26.89</v>
+        <v>4.52</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -990,10 +990,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>5543</v>
+        <v>6613</v>
       </c>
       <c r="B15" t="str">
-        <v>桓鼎股份有限公司</v>
+        <v>朋億*</v>
       </c>
       <c r="C15" t="str">
         <v>上櫃公司</v>
@@ -1002,80 +1002,80 @@
         <v>11508</v>
       </c>
       <c r="E15" t="str">
-        <v>227,256</v>
+        <v>1,690,642</v>
       </c>
       <c r="F15" t="str">
-        <v>211,978</v>
+        <v>589,449</v>
       </c>
       <c r="G15" t="str">
-        <v>15,278</v>
+        <v>1,101,193</v>
       </c>
       <c r="H15" t="str">
-        <v>7.21</v>
+        <v>186.82</v>
       </c>
       <c r="I15" t="str">
-        <v>2,141,825</v>
+        <v>9,111,592</v>
       </c>
       <c r="J15" t="str">
-        <v>2,049,112</v>
+        <v>5,568,748</v>
       </c>
       <c r="K15" t="str">
-        <v>92,713</v>
+        <v>3,542,844</v>
       </c>
       <c r="L15" t="str">
-        <v>4.52</v>
+        <v>63.62</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>營收增加主係半導體廠擴廠暢旺</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>6613</v>
+        <v>6977</v>
       </c>
       <c r="B16" t="str">
-        <v>朋億股份有限公司</v>
+        <v>聯純</v>
       </c>
       <c r="C16" t="str">
-        <v>上櫃公司</v>
+        <v>興櫃公司</v>
       </c>
       <c r="D16" t="str">
         <v>11508</v>
       </c>
       <c r="E16" t="str">
-        <v>1,690,642</v>
+        <v>196,908</v>
       </c>
       <c r="F16" t="str">
-        <v>589,449</v>
+        <v>144,562</v>
       </c>
       <c r="G16" t="str">
-        <v>1,101,193</v>
+        <v>52,346</v>
       </c>
       <c r="H16" t="str">
-        <v>186.82</v>
+        <v>36.21</v>
       </c>
       <c r="I16" t="str">
-        <v>9,111,592</v>
+        <v>1,059,087</v>
       </c>
       <c r="J16" t="str">
-        <v>5,568,748</v>
+        <v>1,431,658</v>
       </c>
       <c r="K16" t="str">
-        <v>3,542,844</v>
+        <v>-372,571</v>
       </c>
       <c r="L16" t="str">
-        <v>63.62</v>
+        <v>-26.02</v>
       </c>
       <c r="M16" t="str">
-        <v>營收增加主係半導體廠擴廠暢旺</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>6977</v>
+        <v>6938</v>
       </c>
       <c r="B17" t="str">
-        <v>聯純科技股份有限公司</v>
+        <v>藍新資訊</v>
       </c>
       <c r="C17" t="str">
         <v>興櫃公司</v>
@@ -1084,28 +1084,28 @@
         <v>11508</v>
       </c>
       <c r="E17" t="str">
-        <v>196,908</v>
+        <v>59,250</v>
       </c>
       <c r="F17" t="str">
-        <v>144,562</v>
+        <v>41,222</v>
       </c>
       <c r="G17" t="str">
-        <v>52,346</v>
+        <v>18,028</v>
       </c>
       <c r="H17" t="str">
-        <v>36.21</v>
+        <v>43.73</v>
       </c>
       <c r="I17" t="str">
-        <v>1,059,087</v>
+        <v>429,476</v>
       </c>
       <c r="J17" t="str">
-        <v>1,431,658</v>
+        <v>340,212</v>
       </c>
       <c r="K17" t="str">
-        <v>-372,571</v>
+        <v>89,264</v>
       </c>
       <c r="L17" t="str">
-        <v>-26.02</v>
+        <v>26.24</v>
       </c>
       <c r="M17" t="str">
         <v/>
@@ -1113,40 +1113,40 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>6938</v>
+        <v>2248</v>
       </c>
       <c r="B18" t="str">
-        <v>藍新資訊股份有限公司</v>
+        <v>華勝-KY</v>
       </c>
       <c r="C18" t="str">
-        <v>興櫃公司</v>
+        <v>上市公司</v>
       </c>
       <c r="D18" t="str">
         <v>11508</v>
       </c>
       <c r="E18" t="str">
-        <v>59,250</v>
+        <v>246,526</v>
       </c>
       <c r="F18" t="str">
-        <v>41,222</v>
+        <v>151,780</v>
       </c>
       <c r="G18" t="str">
-        <v>18,028</v>
+        <v>94,746</v>
       </c>
       <c r="H18" t="str">
-        <v>43.73</v>
+        <v>62.42</v>
       </c>
       <c r="I18" t="str">
-        <v>429,476</v>
+        <v>1,811,034</v>
       </c>
       <c r="J18" t="str">
-        <v>340,212</v>
+        <v>1,198,363</v>
       </c>
       <c r="K18" t="str">
-        <v>89,264</v>
+        <v>612,671</v>
       </c>
       <c r="L18" t="str">
-        <v>26.24</v>
+        <v>51.13</v>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -1154,40 +1154,40 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2248</v>
+        <v>7455</v>
       </c>
       <c r="B19" t="str">
-        <v>華勝汽車電子股份有限公司</v>
+        <v>樺緯物聯</v>
       </c>
       <c r="C19" t="str">
-        <v>上市公司</v>
+        <v>興櫃公司</v>
       </c>
       <c r="D19" t="str">
         <v>11508</v>
       </c>
       <c r="E19" t="str">
-        <v>246,526</v>
+        <v>80,308</v>
       </c>
       <c r="F19" t="str">
-        <v>151,780</v>
+        <v>60,840</v>
       </c>
       <c r="G19" t="str">
-        <v>94,746</v>
+        <v>19,468</v>
       </c>
       <c r="H19" t="str">
-        <v>62.42</v>
+        <v>32.00</v>
       </c>
       <c r="I19" t="str">
-        <v>1,811,034</v>
+        <v>454,995</v>
       </c>
       <c r="J19" t="str">
-        <v>1,198,363</v>
+        <v>575,883</v>
       </c>
       <c r="K19" t="str">
-        <v>612,671</v>
+        <v>-120,888</v>
       </c>
       <c r="L19" t="str">
-        <v>51.13</v>
+        <v>-20.99</v>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -1195,51 +1195,51 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>7455</v>
+        <v>8045</v>
       </c>
       <c r="B20" t="str">
-        <v>樺緯物聯股份有限公司</v>
+        <v>達運光電</v>
       </c>
       <c r="C20" t="str">
-        <v>興櫃公司</v>
+        <v>上市公司</v>
       </c>
       <c r="D20" t="str">
         <v>11508</v>
       </c>
       <c r="E20" t="str">
-        <v>80,308</v>
+        <v>132,509</v>
       </c>
       <c r="F20" t="str">
-        <v>60,840</v>
+        <v>107,371</v>
       </c>
       <c r="G20" t="str">
-        <v>19,468</v>
+        <v>25,138</v>
       </c>
       <c r="H20" t="str">
-        <v>32.00</v>
+        <v>23.41</v>
       </c>
       <c r="I20" t="str">
-        <v>454,995</v>
+        <v>1,192,072</v>
       </c>
       <c r="J20" t="str">
-        <v>575,883</v>
+        <v>892,448</v>
       </c>
       <c r="K20" t="str">
-        <v>-120,888</v>
+        <v>299,624</v>
       </c>
       <c r="L20" t="str">
-        <v>-20.99</v>
+        <v>33.57</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>產品品項增換</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>8045</v>
+        <v>2429</v>
       </c>
       <c r="B21" t="str">
-        <v>達運光電股份有限公司</v>
+        <v>銘旺科</v>
       </c>
       <c r="C21" t="str">
         <v>上市公司</v>
@@ -1248,151 +1248,151 @@
         <v>11508</v>
       </c>
       <c r="E21" t="str">
-        <v>132,509</v>
+        <v>28,303</v>
       </c>
       <c r="F21" t="str">
-        <v>107,371</v>
+        <v>31,173</v>
       </c>
       <c r="G21" t="str">
-        <v>25,138</v>
+        <v>-2,870</v>
       </c>
       <c r="H21" t="str">
-        <v>23.41</v>
+        <v>-9.21</v>
       </c>
       <c r="I21" t="str">
-        <v>1,192,072</v>
+        <v>263,494</v>
       </c>
       <c r="J21" t="str">
-        <v>892,448</v>
+        <v>283,424</v>
       </c>
       <c r="K21" t="str">
-        <v>299,624</v>
+        <v>-19,930</v>
       </c>
       <c r="L21" t="str">
-        <v>33.57</v>
+        <v>-7.03</v>
       </c>
       <c r="M21" t="str">
-        <v>產品品項增換</v>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2429</v>
+        <v>8096</v>
       </c>
       <c r="B22" t="str">
-        <v>銘旺科技股份有限公司</v>
+        <v>擎亞</v>
       </c>
       <c r="C22" t="str">
-        <v>上市公司</v>
+        <v>上櫃公司</v>
       </c>
       <c r="D22" t="str">
         <v>11508</v>
       </c>
       <c r="E22" t="str">
-        <v>28,303</v>
+        <v>7,264,099</v>
       </c>
       <c r="F22" t="str">
-        <v>31,173</v>
+        <v>1,965,621</v>
       </c>
       <c r="G22" t="str">
-        <v>-2,870</v>
+        <v>5,298,478</v>
       </c>
       <c r="H22" t="str">
-        <v>-9.21</v>
+        <v>269.56</v>
       </c>
       <c r="I22" t="str">
-        <v>263,494</v>
+        <v>45,161,685</v>
       </c>
       <c r="J22" t="str">
-        <v>283,424</v>
+        <v>24,998,502</v>
       </c>
       <c r="K22" t="str">
-        <v>-19,930</v>
+        <v>20,163,183</v>
       </c>
       <c r="L22" t="str">
-        <v>-7.03</v>
+        <v>80.66</v>
       </c>
       <c r="M22" t="str">
-        <v/>
+        <v>因伺服器記憶體出貨量增加，致使營收較去年同期成長</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>8096</v>
+        <v>7847</v>
       </c>
       <c r="B23" t="str">
-        <v>擎亞電子股份有限公司</v>
+        <v>豊漁</v>
       </c>
       <c r="C23" t="str">
-        <v>上櫃公司</v>
+        <v>興櫃公司</v>
       </c>
       <c r="D23" t="str">
         <v>11508</v>
       </c>
       <c r="E23" t="str">
-        <v>7,264,099</v>
+        <v>104,158</v>
       </c>
       <c r="F23" t="str">
-        <v>1,965,621</v>
+        <v>83,839</v>
       </c>
       <c r="G23" t="str">
-        <v>5,298,478</v>
+        <v>20,319</v>
       </c>
       <c r="H23" t="str">
-        <v>269.56</v>
+        <v>24.24</v>
       </c>
       <c r="I23" t="str">
-        <v>45,161,685</v>
+        <v>776,959</v>
       </c>
       <c r="J23" t="str">
-        <v>24,998,502</v>
+        <v>648,237</v>
       </c>
       <c r="K23" t="str">
-        <v>20,163,183</v>
+        <v>128,722</v>
       </c>
       <c r="L23" t="str">
-        <v>80.66</v>
+        <v>19.86</v>
       </c>
       <c r="M23" t="str">
-        <v>因伺服器記憶體出貨量增加，致使營收較去年同期成長</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>7847</v>
+        <v>4441</v>
       </c>
       <c r="B24" t="str">
-        <v>豊漁股份有限公司</v>
+        <v>振大環球</v>
       </c>
       <c r="C24" t="str">
-        <v>興櫃公司</v>
+        <v>上市公司</v>
       </c>
       <c r="D24" t="str">
         <v>11508</v>
       </c>
       <c r="E24" t="str">
-        <v>104,158</v>
+        <v>802,332</v>
       </c>
       <c r="F24" t="str">
-        <v>83,839</v>
+        <v>665,511</v>
       </c>
       <c r="G24" t="str">
-        <v>20,319</v>
+        <v>136,821</v>
       </c>
       <c r="H24" t="str">
-        <v>24.24</v>
+        <v>20.56</v>
       </c>
       <c r="I24" t="str">
-        <v>776,959</v>
+        <v>5,582,634</v>
       </c>
       <c r="J24" t="str">
-        <v>648,237</v>
+        <v>4,864,764</v>
       </c>
       <c r="K24" t="str">
-        <v>128,722</v>
+        <v>717,870</v>
       </c>
       <c r="L24" t="str">
-        <v>19.86</v>
+        <v>14.76</v>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -1400,40 +1400,40 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>4441</v>
+        <v>7854</v>
       </c>
       <c r="B25" t="str">
-        <v>振大環球股份有限公司</v>
+        <v>佐茂</v>
       </c>
       <c r="C25" t="str">
-        <v>上市公司</v>
+        <v>興櫃公司</v>
       </c>
       <c r="D25" t="str">
         <v>11508</v>
       </c>
       <c r="E25" t="str">
-        <v>802,332</v>
+        <v>180,157</v>
       </c>
       <c r="F25" t="str">
-        <v>665,511</v>
+        <v>122,419</v>
       </c>
       <c r="G25" t="str">
-        <v>136,821</v>
+        <v>57,738</v>
       </c>
       <c r="H25" t="str">
-        <v>20.56</v>
+        <v>47.16</v>
       </c>
       <c r="I25" t="str">
-        <v>5,582,634</v>
+        <v>1,250,543</v>
       </c>
       <c r="J25" t="str">
-        <v>4,864,764</v>
+        <v>1,090,807</v>
       </c>
       <c r="K25" t="str">
-        <v>717,870</v>
+        <v>159,736</v>
       </c>
       <c r="L25" t="str">
-        <v>14.76</v>
+        <v>14.64</v>
       </c>
       <c r="M25" t="str">
         <v/>
@@ -1441,51 +1441,51 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>7854</v>
+        <v>2330</v>
       </c>
       <c r="B26" t="str">
-        <v>佐茂股份有限公司</v>
+        <v>台積電</v>
       </c>
       <c r="C26" t="str">
-        <v>興櫃公司</v>
+        <v>上市公司</v>
       </c>
       <c r="D26" t="str">
         <v>11508</v>
       </c>
       <c r="E26" t="str">
-        <v>180,157</v>
+        <v>514,805,337</v>
       </c>
       <c r="F26" t="str">
-        <v>122,419</v>
+        <v>335,771,691</v>
       </c>
       <c r="G26" t="str">
-        <v>57,738</v>
+        <v>179,033,646</v>
       </c>
       <c r="H26" t="str">
-        <v>47.16</v>
+        <v>53.32</v>
       </c>
       <c r="I26" t="str">
-        <v>1,250,543</v>
+        <v>3,386,869,575</v>
       </c>
       <c r="J26" t="str">
-        <v>1,090,807</v>
+        <v>2,431,982,931</v>
       </c>
       <c r="K26" t="str">
-        <v>159,736</v>
+        <v>954,886,644</v>
       </c>
       <c r="L26" t="str">
-        <v>14.64</v>
+        <v>39.26</v>
       </c>
       <c r="M26" t="str">
-        <v/>
+        <v>因先進製程產品需求增加所致。</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2330</v>
+        <v>3135</v>
       </c>
       <c r="B27" t="str">
-        <v>台灣積體電路製造股份有限公司</v>
+        <v>凌航</v>
       </c>
       <c r="C27" t="str">
         <v>上市公司</v>
@@ -1494,39 +1494,39 @@
         <v>11508</v>
       </c>
       <c r="E27" t="str">
-        <v>514,805,337</v>
+        <v>1,827,285</v>
       </c>
       <c r="F27" t="str">
-        <v>335,771,691</v>
+        <v>540,959</v>
       </c>
       <c r="G27" t="str">
-        <v>179,033,646</v>
+        <v>1,286,326</v>
       </c>
       <c r="H27" t="str">
-        <v>53.32</v>
+        <v>237.79</v>
       </c>
       <c r="I27" t="str">
-        <v>3,386,869,575</v>
+        <v>15,056,891</v>
       </c>
       <c r="J27" t="str">
-        <v>2,431,982,931</v>
+        <v>4,350,127</v>
       </c>
       <c r="K27" t="str">
-        <v>954,886,644</v>
+        <v>10,706,764</v>
       </c>
       <c r="L27" t="str">
-        <v>39.26</v>
+        <v>246.13</v>
       </c>
       <c r="M27" t="str">
-        <v>因先進製程產品需求增加所致。</v>
+        <v>市場價格上漲及需求增加。</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>3135</v>
+        <v>8112</v>
       </c>
       <c r="B28" t="str">
-        <v>凌航科技股份有限公司</v>
+        <v>至上</v>
       </c>
       <c r="C28" t="str">
         <v>上市公司</v>
@@ -1535,77 +1535,36 @@
         <v>11508</v>
       </c>
       <c r="E28" t="str">
-        <v>1,827,285</v>
+        <v>40,741,046</v>
       </c>
       <c r="F28" t="str">
-        <v>540,959</v>
+        <v>15,987,240</v>
       </c>
       <c r="G28" t="str">
-        <v>1,286,326</v>
+        <v>24,753,806</v>
       </c>
       <c r="H28" t="str">
-        <v>237.79</v>
+        <v>154.83</v>
       </c>
       <c r="I28" t="str">
-        <v>15,056,891</v>
+        <v>378,389,981</v>
       </c>
       <c r="J28" t="str">
-        <v>4,350,127</v>
+        <v>136,396,413</v>
       </c>
       <c r="K28" t="str">
-        <v>10,706,764</v>
+        <v>241,993,568</v>
       </c>
       <c r="L28" t="str">
-        <v>246.13</v>
+        <v>177.42</v>
       </c>
       <c r="M28" t="str">
-        <v>市場價格上漲及需求增加。</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>8112</v>
-      </c>
-      <c r="B29" t="str">
-        <v>至上電子股份有限公司</v>
-      </c>
-      <c r="C29" t="str">
-        <v>上市公司</v>
-      </c>
-      <c r="D29" t="str">
-        <v>11508</v>
-      </c>
-      <c r="E29" t="str">
-        <v>40,741,046</v>
-      </c>
-      <c r="F29" t="str">
-        <v>15,987,240</v>
-      </c>
-      <c r="G29" t="str">
-        <v>24,753,806</v>
-      </c>
-      <c r="H29" t="str">
-        <v>154.83</v>
-      </c>
-      <c r="I29" t="str">
-        <v>378,389,981</v>
-      </c>
-      <c r="J29" t="str">
-        <v>136,396,413</v>
-      </c>
-      <c r="K29" t="str">
-        <v>241,993,568</v>
-      </c>
-      <c r="L29" t="str">
-        <v>177.42</v>
-      </c>
-      <c r="M29" t="str">
         <v>營收大幅成長，主要係記憶體等零組件價格持續上漲，伺服器及手機客戶拉貨動能強勁所致。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M28"/>
   </ignoredErrors>
 </worksheet>
 </file>